--- a/public/templates/forms/A-173-AccountToRoleAssignmentRegister-FORM.xlsx
+++ b/public/templates/forms/A-173-AccountToRoleAssignmentRegister-FORM.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="29920" windowHeight="20380" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="29920" windowHeight="20380" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Register!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -16,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -196,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -256,6 +261,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -606,7 +614,7 @@
       <c r="F6" s="19" t="n"/>
       <c r="G6" s="18" t="n"/>
     </row>
-    <row r="7" ht="32" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Review cadence</t>
@@ -630,14 +638,14 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>« Add one row per item. These columns are the standard minimum every register inherits; add columns this specific register needs (e.g., make/model, version, location for an asset inventory). »</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Username / ID</t>
@@ -780,7 +788,6 @@
       <c r="B24" s="20" t="n"/>
       <c r="C24" s="13">
         <f>COUNTA(A12:A21)</f>
-        <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -792,7 +799,6 @@
       <c r="B25" s="20" t="n"/>
       <c r="C25" s="13">
         <f>COUNTIF(E12:E21,"Active")</f>
-        <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -804,7 +810,6 @@
       <c r="B26" s="20" t="n"/>
       <c r="C26" s="13">
         <f>COUNTIF(E12:E21,"Suspended")</f>
-        <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
@@ -816,7 +821,6 @@
       <c r="B27" s="20" t="n"/>
       <c r="C27" s="13">
         <f>COUNTIF(E12:E21,"Departed")</f>
-        <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
@@ -833,7 +837,6 @@
       <c r="B29" s="20" t="n"/>
       <c r="C29" s="13">
         <f>COUNTIF(G12:G21,"&lt;"&amp;TODAY())</f>
-        <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
@@ -1034,7 +1037,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1042,7 +1045,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
@@ -1067,7 +1070,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, Source Authority, signatures and revision history live on the Register tab.</t>
@@ -1147,7 +1150,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="50.5" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Assigned role(s) &amp; resulting system access</t>
@@ -1169,7 +1172,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Supervisor / approver (role)</t>
@@ -1213,7 +1216,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Last reconciled / Next review due</t>
@@ -1235,7 +1238,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Next Review Due</t>
@@ -1251,13 +1254,11 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="29.75" customHeight="1">
+      <c r="D13" s="25">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="15" ht="34.7" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>« Summary on the Register tab counts entries by status and flags any past their Next Review Due date. Extend the COUNTIF formulas if you add status values. »</t>
@@ -1340,6 +1341,6 @@
     <mergeCell ref="B22:D22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>